--- a/CONVERT/Convert JSON To Excel/CSharp(C#)/Convert JSON To Excel/sample.xlsx
+++ b/CONVERT/Convert JSON To Excel/CSharp(C#)/Convert JSON To Excel/sample.xlsx
@@ -15,33 +15,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Country</t>
   </si>
   <si>
     <t>Age</t>
   </si>
   <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Alice</t>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>Male</t>
   </si>
   <si>
     <t>USA</t>
   </si>
   <si>
-    <t>Bob</t>
+    <t>2025-05-03</t>
+  </si>
+  <si>
+    <t>A001</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Female</t>
   </si>
   <si>
     <t>UK</t>
   </si>
   <si>
-    <t>Charlie</t>
-  </si>
-  <si>
-    <t>Canada</t>
+    <t>2025-05-02</t>
+  </si>
+  <si>
+    <t>A002</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Mendez</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>A003</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Ivanova</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>2025-04-30</t>
+  </si>
+  <si>
+    <t>A004</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>Wei</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>A005</t>
   </si>
 </sst>
 </file>
@@ -494,16 +569,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ef98446-d98a-4603-8ce9-19a4541aa0a5}">
-  <dimension ref="B2:D5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{c7153d45-6f40-4183-a01c-ef6ac63364cd}">
+  <dimension ref="B2:H7"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="4.85714285714286" customWidth="1"/>
-    <col min="4" max="4" width="8.28571428571429" customWidth="1"/>
+    <col min="2" max="2" width="10.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="10.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="8.28571428571429" customWidth="1"/>
+    <col min="6" max="6" width="4.85714285714286" customWidth="1"/>
+    <col min="7" max="7" width="10.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="5.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="12.75">
+    <row r="2" spans="2:8" ht="12.75">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,38 +592,132 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="2:4" ht="12.75">
+    <row r="3" spans="2:8" ht="12.75">
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="12.75">
+    <row r="4" spans="2:8" ht="12.75">
       <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="12.75">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="12.75">
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
-        <v>6</v>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="12.75">
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
+    <row r="7" spans="2:8" ht="12.75">
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
